--- a/reports/Transacciones_Reporte_Completo_Global.xlsx
+++ b/reports/Transacciones_Reporte_Completo_Global.xlsx
@@ -8,11 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen General" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top_30_Productos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribucion_Mensual" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribucion_Semanal" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribucion_Tiendas" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frecuencia_Clientes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top_10_Productos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top_10_Clientes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top_10_Categorias" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribucion_Mensual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribucion_Semanal" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribucion_Tiendas" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiempo_Entre_Compras" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cohortes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retencion" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast_Global" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast_Tiendas" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,13 +552,761 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>cohort_month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.6831</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6935</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6726</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6754</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2013-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2013-05-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2752</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>yhat</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>184831.1666666667</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>184831.1666666667</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>184831.1666666667</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>184831.1666666667</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2013-11-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>184831.1666666667</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>184831.1666666667</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>store_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>yhat</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>52381</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>52381</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>52381</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>52381</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2013-11-01</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>52381</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>52381</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>67855</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>103</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>67855</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>67855</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>103</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>67855</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>103</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2013-11-01</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>67855</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>103</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>67855</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>107</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>42438.83333333334</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>107</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>42438.83333333334</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>107</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>42438.83333333334</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>107</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>42438.83333333334</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>107</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2013-11-01</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>42438.83333333334</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>107</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>42438.83333333334</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>110</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2013-07-01</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>22156.33333333333</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>110</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>22156.33333333333</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>110</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>22156.33333333333</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>110</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>22156.33333333333</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>110</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2013-11-01</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>22156.33333333333</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>110</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2013-12-01</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>22156.33333333333</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Naive-Seasonal-Avg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,226 +1434,6 @@
       </c>
       <c r="C11" t="n">
         <v>2.01</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B12" t="n">
-        <v>210081</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>202214</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>185167</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>19</v>
-      </c>
-      <c r="B15" t="n">
-        <v>183467</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>179634</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>173154</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>166405</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>166233</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>26</v>
-      </c>
-      <c r="B20" t="n">
-        <v>151794</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>23</v>
-      </c>
-      <c r="B21" t="n">
-        <v>145956</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="n">
-        <v>141429</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="n">
-        <v>136176</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>30</v>
-      </c>
-      <c r="B24" t="n">
-        <v>133878</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>32</v>
-      </c>
-      <c r="B25" t="n">
-        <v>130965</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>28</v>
-      </c>
-      <c r="B26" t="n">
-        <v>126722</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" t="n">
-        <v>122922</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" t="n">
-        <v>121363</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="n">
-        <v>113850</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="n">
-        <v>113668</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" t="n">
-        <v>113246</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1.07</v>
       </c>
     </row>
   </sheetData>
@@ -913,113 +1447,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>customer_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>month</t>
+          <t>frecuencia_absoluta</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>num_transacciones</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>porcentaje</t>
+          <t>frecuencia_relativa_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2013</v>
+        <v>336296</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>535</v>
       </c>
       <c r="C2" t="n">
-        <v>184916</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16.67</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2013</v>
+        <v>440157</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>163</v>
       </c>
       <c r="C3" t="n">
-        <v>170771</v>
-      </c>
-      <c r="D3" t="n">
-        <v>15.4</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2013</v>
+        <v>806377</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="C4" t="n">
-        <v>189313</v>
-      </c>
-      <c r="D4" t="n">
-        <v>17.07</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2013</v>
+        <v>576930</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>157</v>
       </c>
       <c r="C5" t="n">
-        <v>182632</v>
-      </c>
-      <c r="D5" t="n">
-        <v>16.47</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2013</v>
+        <v>525328</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>149</v>
       </c>
       <c r="C6" t="n">
-        <v>188199</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16.97</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2013</v>
+        <v>307063</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>193156</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17.42</v>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>517807</v>
+      </c>
+      <c r="B8" t="n">
+        <v>144</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>908225</v>
+      </c>
+      <c r="B9" t="n">
+        <v>134</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>51733</v>
+      </c>
+      <c r="B10" t="n">
+        <v>130</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>212565</v>
+      </c>
+      <c r="B11" t="n">
+        <v>129</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -1033,115 +1588,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>dia_semana</t>
+          <t>category_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>num_transacciones</t>
+          <t>category_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>unidades_vendidas</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>porcentaje</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Domingo</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>191406</v>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>17.26</v>
+        <v>5330800</v>
+      </c>
+      <c r="D2" t="n">
+        <v>34.91</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Lunes</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>142445</v>
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VERDURAS RAIZ,TUBERCULO Y BULBOS</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>12.84</v>
+        <v>1811523</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.86</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Martes</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>150739</v>
+      <c r="A4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CARNES PROCESADAS AL VACIO</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>13.59</v>
+        <v>1811523</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.86</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Miércoles</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>137245</v>
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VERDURAS DE FRUTOS</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>12.38</v>
+        <v>1410750</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.24</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Jueves</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>158766</v>
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CUIDADO DE LA ROPA</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>14.32</v>
+        <v>1410750</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.24</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Viernes</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>139371</v>
+      <c r="A7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JUGOS</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>12.57</v>
+        <v>729513</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.78</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sábado</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>189015</v>
+      <c r="A8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VERDURAS DE HOJAS</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>17.04</v>
+        <v>729513</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AROMATICAS CONDIMENTOS</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>493388</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PASTAS COMESTIBLES</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>491896</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AROMATICAS MEDICINALES</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>294753</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>
@@ -1155,21 +1778,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>store_id</t>
+          <t>year</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>num_transacciones</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>porcentaje</t>
         </is>
@@ -1177,46 +1805,86 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103</v>
+        <v>2013</v>
       </c>
       <c r="B2" t="n">
-        <v>407130</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.71</v>
+        <v>184916</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102</v>
+        <v>2013</v>
       </c>
       <c r="B3" t="n">
-        <v>314286</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.34</v>
+        <v>170771</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107</v>
+        <v>2013</v>
       </c>
       <c r="B4" t="n">
-        <v>254633</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.96</v>
+        <v>189313</v>
+      </c>
+      <c r="D4" t="n">
+        <v>17.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110</v>
+        <v>2013</v>
       </c>
       <c r="B5" t="n">
-        <v>132938</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.99</v>
+        <v>182632</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16.47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>188199</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>193156</v>
+      </c>
+      <c r="D7" t="n">
+        <v>17.42</v>
       </c>
     </row>
   </sheetData>
@@ -1230,244 +1898,302 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>num_compras</t>
+          <t>dia_semana</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>num_clientes</t>
+          <t>num_transacciones</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>porcentaje_clientes</t>
+          <t>porcentaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Domingo</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>191406</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17.26</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lunes</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>142445</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Martes</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>150739</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13.59</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Miércoles</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>137245</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12.38</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jueves</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>158766</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14.32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Viernes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>139371</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12.57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sábado</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>189015</v>
+      </c>
+      <c r="C8" t="n">
+        <v>17.04</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>store_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>num_transacciones</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>porcentaje</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="B2" t="n">
-        <v>34513</v>
+        <v>407130</v>
       </c>
       <c r="C2" t="n">
-        <v>26.31</v>
+        <v>36.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="B3" t="n">
-        <v>16182</v>
+        <v>314286</v>
       </c>
       <c r="C3" t="n">
-        <v>12.34</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>107</v>
       </c>
       <c r="B4" t="n">
-        <v>10613</v>
+        <v>254633</v>
       </c>
       <c r="C4" t="n">
-        <v>8.09</v>
+        <v>22.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="B5" t="n">
-        <v>8124</v>
+        <v>132938</v>
       </c>
       <c r="C5" t="n">
-        <v>6.19</v>
+        <v>11.99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>promedio_global_dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>26.39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>cohort_month</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cohort_size</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>71549</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2013-02-01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>19680</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2013-03-01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14069</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9443</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2013-05-01</t>
+        </is>
       </c>
       <c r="B6" t="n">
-        <v>6642</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5.06</v>
+        <v>8293</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2013-06-01</t>
+        </is>
       </c>
       <c r="B7" t="n">
-        <v>5678</v>
-      </c>
-      <c r="C7" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4072</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3598</v>
-      </c>
-      <c r="C10" t="n">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3176</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2885</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2548</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2294</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2152</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1868</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1683</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1578</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1528</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>1261</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1175</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.9</v>
+        <v>8152</v>
       </c>
     </row>
   </sheetData>
